--- a/data/trans_orig/Q33-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Habitat-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según las horas al día que duerme habitualmente</t>
+          <t>Población según las horas al día que duerme habitualmente (tasa de respuesta: 98,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,7 +716,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,54; 7,69</t>
+          <t>7,53; 7,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,5; 7,68</t>
+          <t>7,49; 7,68</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,29</t>
+          <t>7,11; 7,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,21</t>
+          <t>7,0; 7,19</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,12 +751,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 7,01</t>
+          <t>6,86; 7,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,56</t>
+          <t>7,45; 7,57</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,51</t>
+          <t>7,36; 7,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,12</t>
+          <t>7,0; 7,13</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,52; 7,67</t>
+          <t>7,51; 7,67</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,51</t>
+          <t>7,36; 7,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,27</t>
+          <t>7,23; 8,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,3; 7,46</t>
+          <t>7,31; 7,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,38</t>
+          <t>7,25; 7,37</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,94</t>
+          <t>7,16; 7,91</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,53</t>
+          <t>7,35; 7,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7,35; 7,54</t>
+          <t>7,36; 7,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,4; 7,58</t>
+          <t>7,41; 7,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,26</t>
+          <t>7,06; 7,28</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 7,32</t>
+          <t>7,12; 7,32</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,37</t>
+          <t>7,19; 7,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 7,11</t>
+          <t>6,47; 7,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,44</t>
+          <t>7,33; 7,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,63; 7,14</t>
+          <t>6,62; 7,15</t>
         </is>
       </c>
     </row>
@@ -1141,42 +1141,42 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,45</t>
+          <t>7,28; 7,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,5</t>
+          <t>7,32; 7,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,98; 7,16</t>
+          <t>6,99; 7,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,58</t>
+          <t>7,42; 7,58</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,21</t>
+          <t>7,05; 7,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 7,34</t>
+          <t>7,19; 7,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 7,09</t>
+          <t>6,95; 7,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,45; 7,56</t>
+          <t>7,46; 7,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,09</t>
+          <t>6,99; 7,1</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,43; 7,51</t>
+          <t>7,42; 7,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,69</t>
+          <t>7,15; 7,66</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,17 +1301,17 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,14; 7,23</t>
+          <t>7,13; 7,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,21; 7,29</t>
+          <t>7,2; 7,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,8; 7,05</t>
+          <t>6,78; 7,05</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,31</t>
+          <t>7,25; 7,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,04; 7,34</t>
+          <t>7,03; 7,36</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q33-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q33-Habitat-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>7,18</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>6,93</t>
+          <t>6,94</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -716,37 +716,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 7,68</t>
+          <t>7,54; 7,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>7,27; 7,47</t>
+          <t>7,27; 7,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,49; 7,68</t>
+          <t>7,5; 7,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,11; 7,3</t>
+          <t>7,09; 7,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,32; 7,49</t>
+          <t>7,33; 7,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,19</t>
+          <t>7,01; 7,21</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 7,38</t>
+          <t>7,17; 7,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>7,0; 7,13</t>
+          <t>7,0; 7,12</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,62</t>
+          <t>7,26</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,1</t>
+          <t>7,12</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,39</t>
+          <t>7,19</t>
         </is>
       </c>
     </row>
@@ -856,42 +856,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 7,67</t>
+          <t>7,52; 7,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,47</t>
+          <t>7,3; 7,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,36; 7,49</t>
+          <t>7,36; 7,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,23; 8,37</t>
+          <t>7,19; 7,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,31; 7,46</t>
+          <t>7,3; 7,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,33</t>
+          <t>7,15; 7,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,28</t>
+          <t>7,12; 7,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,16</t>
+          <t>7,05; 7,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,37</t>
+          <t>7,26; 7,38</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,91</t>
+          <t>7,14; 7,24</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,84</t>
+          <t>7,09</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,97</t>
+          <t>7,12</t>
         </is>
       </c>
     </row>
@@ -996,42 +996,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>7,36; 7,53</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>7,35; 7,54</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>7,36; 7,55</t>
-        </is>
-      </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,41; 7,58</t>
+          <t>7,4; 7,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 7,28</t>
+          <t>7,07; 7,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,12; 7,32</t>
+          <t>7,13; 7,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>7,16; 7,34</t>
+          <t>7,15; 7,34</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 7,37</t>
+          <t>7,18; 7,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,47; 7,11</t>
+          <t>7,01; 7,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1041,17 +1041,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,42</t>
+          <t>7,27; 7,41</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,45</t>
+          <t>7,32; 7,45</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,62; 7,15</t>
+          <t>7,06; 7,19</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,07</t>
+          <t>7,08</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 7,44</t>
+          <t>7,28; 7,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,16</t>
+          <t>7,0; 7,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,58</t>
+          <t>7,44; 7,59</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,05; 7,22</t>
+          <t>7,05; 7,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,95; 7,08</t>
+          <t>6,94; 7,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 7,1</t>
+          <t>6,99; 7,09</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,3</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6,98</t>
+          <t>7,04</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7,13</t>
+          <t>7,11</t>
         </is>
       </c>
     </row>
@@ -1281,17 +1281,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 7,44</t>
+          <t>7,35; 7,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,42; 7,51</t>
+          <t>7,43; 7,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,15; 7,66</t>
+          <t>7,13; 7,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1301,37 +1301,37 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,13; 7,23</t>
+          <t>7,14; 7,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 7,29</t>
+          <t>7,21; 7,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,78; 7,05</t>
+          <t>7,01; 7,08</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,44; 7,49</t>
+          <t>7,43; 7,49</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7,25; 7,32</t>
+          <t>7,26; 7,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7,33; 7,39</t>
+          <t>7,32; 7,39</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,03; 7,36</t>
+          <t>7,08; 7,13</t>
         </is>
       </c>
     </row>
